--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/COLORADO_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/COLORADO_2013.xlsx
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>0.000957192236107</v>
+        <v>0.0009571922361070002</v>
       </c>
     </row>
     <row r="14">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C140">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C198">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C311">
@@ -6133,7 +6133,7 @@
         <v>18</v>
       </c>
       <c r="D321">
-        <v>0.000957192236107</v>
+        <v>0.0009571922361070002</v>
       </c>
     </row>
     <row r="322">
@@ -6439,7 +6439,7 @@
         <v>18</v>
       </c>
       <c r="D338">
-        <v>0.000957192236107</v>
+        <v>0.0009571922361070002</v>
       </c>
     </row>
     <row r="339">
@@ -9031,7 +9031,7 @@
         <v>18</v>
       </c>
       <c r="D482">
-        <v>0.000957192236107</v>
+        <v>0.0009571922361070002</v>
       </c>
     </row>
     <row r="483">
@@ -12487,7 +12487,7 @@
         <v>18</v>
       </c>
       <c r="D674">
-        <v>0.000957192236107</v>
+        <v>0.0009571922361070002</v>
       </c>
     </row>
     <row r="675">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C716">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C797">
@@ -15547,7 +15547,7 @@
         <v>18</v>
       </c>
       <c r="D844">
-        <v>0.000957192236107</v>
+        <v>0.0009571922361070002</v>
       </c>
     </row>
     <row r="845">
@@ -22207,7 +22207,7 @@
         <v>18</v>
       </c>
       <c r="D1214">
-        <v>0.000957192236107</v>
+        <v>0.0009571922361070002</v>
       </c>
     </row>
     <row r="1215">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1221">
@@ -23251,7 +23251,7 @@
         <v>18</v>
       </c>
       <c r="D1272">
-        <v>0.000957192236107</v>
+        <v>0.0009571922361070002</v>
       </c>
     </row>
     <row r="1273">
